--- a/VibeProject1/Assets/Table/Caravan/Facility.xlsx
+++ b/VibeProject1/Assets/Table/Caravan/Facility.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,6 +428,11 @@
           <t>Price</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -438,6 +443,9 @@
       <c r="B2" t="n">
         <v>1000</v>
       </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -448,6 +456,9 @@
       <c r="B3" t="n">
         <v>1000</v>
       </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -458,6 +469,9 @@
       <c r="B4" t="n">
         <v>1000</v>
       </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -468,6 +482,9 @@
       <c r="B5" t="n">
         <v>1000</v>
       </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -477,6 +494,9 @@
       </c>
       <c r="B6" t="n">
         <v>1000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/VibeProject1/Assets/Table/Caravan/Facility.xlsx
+++ b/VibeProject1/Assets/Table/Caravan/Facility.xlsx
@@ -1,35 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Merchant\VibeProject1\Assets\Table\Caravan\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE140145-CF4C-4F3C-A0F7-A7CB24E592A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="29550" yWindow="1500" windowWidth="21405" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Facility" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="FacilityStrings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Facility" sheetId="1" r:id="rId1"/>
+    <sheet name="FacilityStrings" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>Down</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Facility01</t>
+  </si>
+  <si>
+    <t>Facility02</t>
+  </si>
+  <si>
+    <t>Facility03</t>
+  </si>
+  <si>
+    <t>Facility04</t>
+  </si>
+  <si>
+    <t>Facility05</t>
+  </si>
+  <si>
+    <t>Ko</t>
+  </si>
+  <si>
+    <t>시설이름1</t>
+  </si>
+  <si>
+    <t>시설이름2</t>
+  </si>
+  <si>
+    <t>시설이름3</t>
+  </si>
+  <si>
+    <t>시설이름4</t>
+  </si>
+  <si>
+    <t>시설이름5</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,80 +115,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,183 +417,191 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Facility01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
         <v>1000</v>
       </c>
-      <c r="C2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Facility02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
         <v>1000</v>
       </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Facility03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
         <v>1000</v>
       </c>
-      <c r="C4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Facility04</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
         <v>1000</v>
       </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Facility05</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
         <v>1000</v>
       </c>
-      <c r="C6" t="n">
-        <v>4</v>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Facility01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>시설이름1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Facility02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>시설이름2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Facility03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>시설이름3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Facility04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>시설이름4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Facility05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>시설이름5</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/VibeProject1/Assets/Table/Caravan/Facility.xlsx
+++ b/VibeProject1/Assets/Table/Caravan/Facility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Merchant\VibeProject1\Assets\Table\Caravan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE140145-CF4C-4F3C-A0F7-A7CB24E592A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6426ED8D-5FA0-4CEF-844F-D82597860FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29550" yWindow="1500" windowWidth="21405" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -29,19 +29,13 @@
     <t>Price</t>
   </si>
   <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>Down</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Right</t>
+    <t>AreaShape</t>
   </si>
   <si>
     <t>Facility01</t>
+  </si>
+  <si>
+    <t>1111111/1111111/1111111/1112111/1111111/1111111/1111111</t>
   </si>
   <si>
     <t>Facility02</t>
@@ -418,10 +412,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="59.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -431,114 +428,60 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
       </c>
       <c r="B2">
         <v>1000</v>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>1000</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>1000</v>
       </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>1000</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
+      <c r="C6" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -557,47 +500,47 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/VibeProject1/Assets/Table/Caravan/Facility.xlsx
+++ b/VibeProject1/Assets/Table/Caravan/Facility.xlsx
@@ -1,130 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <x:workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Merchant\VibeProject1\Assets\Table\Caravan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6426ED8D-5FA0-4CEF-844F-D82597860FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="29550" yWindow="1500" windowWidth="21405" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Facility" sheetId="1" r:id="rId1"/>
-    <sheet name="FacilityStrings" sheetId="2" r:id="rId2"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
+  <x:bookViews>
+    <x:workbookView xWindow="29550" yWindow="1500" windowWidth="21405" windowHeight="10770" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Facility" sheetId="1" r:id="rId1"/>
+    <x:sheet name="FacilityStrings" sheetId="2" r:id="rId2"/>
+  </x:sheets>
+  <x:definedNames/>
+  <x:calcPr calcId="0"/>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>AreaShape</t>
-  </si>
-  <si>
-    <t>Facility01</t>
-  </si>
-  <si>
-    <t>1111111/1111111/1111111/1112111/1111111/1111111/1111111</t>
-  </si>
-  <si>
-    <t>Facility02</t>
-  </si>
-  <si>
-    <t>Facility03</t>
-  </si>
-  <si>
-    <t>Facility04</t>
-  </si>
-  <si>
-    <t>Facility05</t>
-  </si>
-  <si>
-    <t>Ko</t>
-  </si>
-  <si>
-    <t>시설이름1</t>
-  </si>
-  <si>
-    <t>시설이름2</t>
-  </si>
-  <si>
-    <t>시설이름3</t>
-  </si>
-  <si>
-    <t>시설이름4</t>
-  </si>
-  <si>
-    <t>시설이름5</t>
-  </si>
-</sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Price</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AreaShape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Facility01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111/1111111/1111111/1112111/1111111/1111111/1111111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Facility02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Facility03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Facility04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Facility05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ko</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시설이름1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시설이름2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시설이름3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시설이름4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시설이름5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDurability</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2 xr">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="0" formatCode=""/>
+  </x:numFmts>
+  <x:fonts count="3" x14ac:knownFonts="1">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="맑은 고딕"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="8"/>
+      <x:name val="맑은 고딕"/>
+      <x:family val="3"/>
+      <x:charset val="129"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="2">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="표준" xfId="0" builtinId="0"/>
+  </x:cellStyles>
+  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+    </x:ext>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
+    </x:ext>
+  </x:extLst>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -411,140 +424,173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="59.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>1000</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1000</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1000</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>1000</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1000</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:C6"/>
+  <x:sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <x:cols>
+    <x:col min="1" max="2" width="9.090625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="59.875" style="0" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D2" s="0">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D3" s="0">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D4" s="0">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:phoneticPr fontId="1" type="noConversion"/>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0100-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B6"/>
+  <x:sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:phoneticPr fontId="1" type="noConversion"/>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>